--- a/Web/TestCasesWeb/Usuarios.xlsx
+++ b/Web/TestCasesWeb/Usuarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FB1F92-2862-458E-A80F-A8D6AA1A0B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D034C8A-9C6A-4C61-A34B-EF0855566C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="117">
   <si>
     <t>Num</t>
   </si>
@@ -888,7 +888,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1565,11 +1565,6 @@
         <v>61</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H33" t="s">
         <v>113</v>
       </c>
     </row>

--- a/Web/TestCasesWeb/Usuarios.xlsx
+++ b/Web/TestCasesWeb/Usuarios.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D034C8A-9C6A-4C61-A34B-EF0855566C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295A3A94-573D-4B79-AA23-657F434C916B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="125">
   <si>
     <t>Num</t>
   </si>
@@ -44,12 +57,6 @@
   </si>
   <si>
     <t>Notes</t>
-  </si>
-  <si>
-    <t>1. Users page home is correctly.</t>
-  </si>
-  <si>
-    <t>Users page home</t>
   </si>
   <si>
     <t>USU001</t>
@@ -210,9 +217,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>BL</t>
   </si>
   <si>
     <t>Create first user, mandatory parameters</t>
@@ -315,11 +319,6 @@
     <t>1 .The rol is updated.</t>
   </si>
   <si>
-    <t>1. The user selects a restaurant
-2. Fills the pin
-3. Clicks "Borrar rol"</t>
-  </si>
-  <si>
     <t>1 .The rol is deleted.</t>
   </si>
   <si>
@@ -356,17 +355,6 @@
   <si>
     <t>1. The user clicks "Nuevo usuario"
 2. Clicks "Cancelar"</t>
-  </si>
-  <si>
-    <t>1. The user selects an user
-2. Clicks the garvage icon
-3. Clicks "Cancelar"</t>
-  </si>
-  <si>
-    <t>1. The user selects an user
-2. Clicks the garvage icon
-3. Modify the user
-4. Clicks "Eliminar"</t>
   </si>
   <si>
     <t>1. The user selects an user
@@ -403,9 +391,6 @@
     <t>1. The password is not shown.</t>
   </si>
   <si>
-    <t>Si haces una búsqueda q no devuelve resultados, se activa "Crear primer usuario" no tiene sentido</t>
-  </si>
-  <si>
     <t>1. The user searchs an user</t>
   </si>
   <si>
@@ -425,13 +410,72 @@
   </si>
   <si>
     <t>1. An error is shown.</t>
+  </si>
+  <si>
+    <t>Users page</t>
+  </si>
+  <si>
+    <t>1. Users page is correctly.</t>
+  </si>
+  <si>
+    <t>No se puede asignar el nuevo rol a Todos los restaurantes: USU001_1.jpg y USU001_2.jpg</t>
+  </si>
+  <si>
+    <t>Internal server error, al crear un usuario. Tal vez es porque ya existía uno con el mismo nombre para otro restaurante: USU002.jpg</t>
+  </si>
+  <si>
+    <t>Delete asigned rol</t>
+  </si>
+  <si>
+    <t>1 .The rol is not deleted
+2. A message is shown</t>
+  </si>
+  <si>
+    <t>El mensaje sale antes de borrarlo, pero al darle a "Eliminar" el mensaje queda fijo y la página bloqueda: USU003.jpg</t>
+  </si>
+  <si>
+    <t>Delete asigned rol, cancel</t>
+  </si>
+  <si>
+    <t>1. The user selects a restaurant
+2. Clicks a rol
+3. Clicks "Borrar rol"</t>
+  </si>
+  <si>
+    <t>1. The user selects a restaurant
+2. Clicks a rol
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The user selects an user
+2. Clicks the garbage icon
+3. Modify the user
+4. Clicks "Eliminar"</t>
+  </si>
+  <si>
+    <t>1. The user selects an user
+2. Clicks the garbage icon
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>USU030</t>
+  </si>
+  <si>
+    <t>USU031</t>
+  </si>
+  <si>
+    <t>Si haces una búsqueda q no devuelve resultados, se activa "Crear primer usuario" no tiene sentido
+Seleccionas un restaurante y en el buscardor el mismo, y no muestra los usuarios existentes: USU004.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -468,13 +512,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -516,12 +553,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -536,16 +570,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -888,14 +934,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="48" customWidth="1"/>
     <col min="4" max="4" width="41.5703125" customWidth="1"/>
     <col min="5" max="6" width="33.42578125" customWidth="1"/>
-    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.42578125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -920,657 +966,705 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:8" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="9"/>
+    </row>
+    <row r="15" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" s="13" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="12"/>
+      <c r="G18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="12"/>
+    </row>
+    <row r="19" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" s="4" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" s="4" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="6"/>
-    </row>
-    <row r="11" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>13</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>15</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>17</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>21</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>22</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H23" s="6"/>
-    </row>
-    <row r="24" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>23</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>24</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>25</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4" t="s">
+      <c r="F32" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="H32" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="1:8" s="5" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <v>27</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="10" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G30">
+  <conditionalFormatting sqref="G2:G32">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
@@ -1584,6 +1678,9 @@
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="H32" r:id="rId1" xr:uid="{F7AE9F79-219C-498C-9EEC-FBE8EA1BBCB1}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Web/TestCasesWeb/Usuarios.xlsx
+++ b/Web/TestCasesWeb/Usuarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295A3A94-573D-4B79-AA23-657F434C916B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{005ABB5E-0D4A-4E24-9247-B2AB9C881E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="0" windowWidth="23265" windowHeight="14145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="124">
   <si>
     <t>Num</t>
   </si>
@@ -75,48 +75,6 @@
 </t>
   </si>
   <si>
-    <t>Modify user</t>
-  </si>
-  <si>
-    <t>Delete user</t>
-  </si>
-  <si>
-    <t>Create rol</t>
-  </si>
-  <si>
-    <t>Modify rol</t>
-  </si>
-  <si>
-    <t>Delete rol</t>
-  </si>
-  <si>
-    <t>Create rol, cancel operation</t>
-  </si>
-  <si>
-    <t>Modify rol, cancel operation</t>
-  </si>
-  <si>
-    <t>Delete rol, cancel operation</t>
-  </si>
-  <si>
-    <t>Create pin</t>
-  </si>
-  <si>
-    <t>Modify pin</t>
-  </si>
-  <si>
-    <t>Delete pin</t>
-  </si>
-  <si>
-    <t>Create pin, cancel operation</t>
-  </si>
-  <si>
-    <t>Modify pin, cancel operation</t>
-  </si>
-  <si>
-    <t>Delete pin, cancel operation</t>
-  </si>
-  <si>
     <t>USU005</t>
   </si>
   <si>
@@ -153,21 +111,6 @@
     <t>USU016</t>
   </si>
   <si>
-    <t>Modify first user</t>
-  </si>
-  <si>
-    <t>Delete first user</t>
-  </si>
-  <si>
-    <t>Create first user, cancel operation</t>
-  </si>
-  <si>
-    <t>Modify first user, cancel operation</t>
-  </si>
-  <si>
-    <t>Delete first user, cancel operation</t>
-  </si>
-  <si>
     <t>USU017</t>
   </si>
   <si>
@@ -186,18 +129,6 @@
     <t>USU022</t>
   </si>
   <si>
-    <t>Change status user</t>
-  </si>
-  <si>
-    <t>See pwd</t>
-  </si>
-  <si>
-    <t>Hide password</t>
-  </si>
-  <si>
-    <t>Search an user</t>
-  </si>
-  <si>
     <t>USU023</t>
   </si>
   <si>
@@ -217,18 +148,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>Create first user, mandatory parameters</t>
-  </si>
-  <si>
-    <t>Create first user, all parameters</t>
-  </si>
-  <si>
-    <t>Create user, mandatory parameters</t>
-  </si>
-  <si>
-    <t>Create user, all parameters</t>
   </si>
   <si>
     <t>USU028</t>
@@ -397,21 +316,12 @@
     <t>1. The user is shown.</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1qPVul8SpdHMaF4rQQy9YfB22DFVzyLtB/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>Create a user after performing a search that returns no results</t>
-  </si>
-  <si>
     <t>1. The user searchs an user
 2. Clicks "create a first user"
 3. Fills the fields
 4. Clicks "Guardar"</t>
   </si>
   <si>
-    <t>1. An error is shown.</t>
-  </si>
-  <si>
     <t>Users page</t>
   </si>
   <si>
@@ -422,9 +332,6 @@
   </si>
   <si>
     <t>Internal server error, al crear un usuario. Tal vez es porque ya existía uno con el mismo nombre para otro restaurante: USU002.jpg</t>
-  </si>
-  <si>
-    <t>Delete asigned rol</t>
   </si>
   <si>
     <t>1 .The rol is not deleted
@@ -432,9 +339,6 @@
   </si>
   <si>
     <t>El mensaje sale antes de borrarlo, pero al darle a "Eliminar" el mensaje queda fijo y la página bloqueda: USU003.jpg</t>
-  </si>
-  <si>
-    <t>Delete asigned rol, cancel</t>
   </si>
   <si>
     <t>1. The user selects a restaurant
@@ -466,6 +370,99 @@
   <si>
     <t>Si haces una búsqueda q no devuelve resultados, se activa "Crear primer usuario" no tiene sentido
 Seleccionas un restaurante y en el buscardor el mismo, y no muestra los usuarios existentes: USU004.jpg</t>
+  </si>
+  <si>
+    <t>Un error aparece: user002.jpg</t>
+  </si>
+  <si>
+    <t>Users: Create, mandatory parameters</t>
+  </si>
+  <si>
+    <t>Users: Create, all parameters</t>
+  </si>
+  <si>
+    <t>Users: Modify</t>
+  </si>
+  <si>
+    <t>Users: Delete</t>
+  </si>
+  <si>
+    <t>Users: Create rol</t>
+  </si>
+  <si>
+    <t>Users: Create rol, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Modify rol</t>
+  </si>
+  <si>
+    <t>Users: Modify rol, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Delete rol</t>
+  </si>
+  <si>
+    <t>Users: Delete rol, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Delete asigned rol</t>
+  </si>
+  <si>
+    <t>Users: Delete asigned rol, cancel</t>
+  </si>
+  <si>
+    <t>Users: Create pin</t>
+  </si>
+  <si>
+    <t>Users: Create pin, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Modify pin</t>
+  </si>
+  <si>
+    <t>Users: Modify pin, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Delete pin</t>
+  </si>
+  <si>
+    <t>Users: Delete pin, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Create first user, mandatory parameters</t>
+  </si>
+  <si>
+    <t>Users: Create first user, all parameters</t>
+  </si>
+  <si>
+    <t>Users: Create first user, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Modify first user</t>
+  </si>
+  <si>
+    <t>Users: Modify first user, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Delete first user</t>
+  </si>
+  <si>
+    <t>Users: Delete first user, cancel operation</t>
+  </si>
+  <si>
+    <t>Users: Change status</t>
+  </si>
+  <si>
+    <t>Users: See pwd</t>
+  </si>
+  <si>
+    <t>Users: Hide password</t>
+  </si>
+  <si>
+    <t>Users: Search</t>
+  </si>
+  <si>
+    <t>Users: Create a user after performing a search that returns no results</t>
   </si>
 </sst>
 </file>
@@ -553,7 +550,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -594,6 +591,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -978,17 +976,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="2"/>
+        <v>81</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="G2" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H2" s="8"/>
     </row>
@@ -1000,15 +1000,15 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H3" s="5"/>
     </row>
@@ -1020,17 +1020,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G4" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H4" s="5"/>
     </row>
@@ -1042,17 +1044,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="G5" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H5" s="2"/>
     </row>
@@ -1061,20 +1065,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F6" s="2"/>
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="G6" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H6" s="2"/>
     </row>
@@ -1083,23 +1089,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="6" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1107,20 +1113,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G8" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -1129,23 +1137,23 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="6" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1153,20 +1161,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F10" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G10" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2"/>
     </row>
@@ -1175,20 +1185,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F11" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G11" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H11" s="2"/>
     </row>
@@ -1197,20 +1209,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G12" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H12" s="2"/>
     </row>
@@ -1219,23 +1233,23 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="6" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -1243,20 +1257,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G14" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H14" s="9"/>
     </row>
@@ -1265,20 +1281,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F15" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="G15" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H15" s="5"/>
     </row>
@@ -1287,20 +1305,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G16" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H16" s="5"/>
     </row>
@@ -1309,20 +1329,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F17" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="G17" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H17" s="2"/>
     </row>
@@ -1331,20 +1353,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F18" s="12"/>
+        <v>43</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>43</v>
+      </c>
       <c r="G18" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H18" s="12"/>
     </row>
@@ -1353,20 +1377,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="G19" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H19" s="2"/>
     </row>
@@ -1375,20 +1401,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G20" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H20" s="2"/>
     </row>
@@ -1397,20 +1425,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="2"/>
+        <v>48</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G21" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H21" s="5"/>
     </row>
@@ -1419,20 +1449,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G22" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H22" s="5"/>
     </row>
@@ -1441,20 +1473,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G23" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H23" s="5"/>
     </row>
@@ -1463,20 +1497,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F24" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="G24" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H24" s="2"/>
     </row>
@@ -1485,20 +1521,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>42</v>
+        <v>116</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G25" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H25" s="2"/>
     </row>
@@ -1507,20 +1545,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="G26" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H26" s="2"/>
     </row>
@@ -1529,20 +1569,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F27" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G27" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H27" s="2"/>
     </row>
@@ -1551,20 +1593,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="G28" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H28" s="2"/>
     </row>
@@ -1573,20 +1617,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F29" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="G29" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H29" s="2"/>
     </row>
@@ -1595,20 +1641,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F30" s="2"/>
+        <v>76</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="G30" s="6" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="H30" s="2"/>
     </row>
@@ -1617,23 +1665,23 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="6" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="4" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1641,25 +1689,23 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>109</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>106</v>
+        <v>36</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1678,9 +1724,6 @@
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="H32" r:id="rId1" xr:uid="{F7AE9F79-219C-498C-9EEC-FBE8EA1BBCB1}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>